--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484037_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484037_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5042</v>
+        <v>2.9415</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9498</v>
+        <v>3.1166</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5543</v>
+        <v>-0.1751</v>
       </c>
       <c r="G2" t="n">
         <v>1.5257</v>
@@ -610,13 +610,13 @@
         <v>1.9838</v>
       </c>
       <c r="S2" t="n">
-        <v>2.359</v>
+        <v>0.7963</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2358</v>
+        <v>0.4026</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1232</v>
+        <v>0.3937</v>
       </c>
       <c r="V2" t="n">
         <v>1.8097</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2774</v>
+        <v>1.8751</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9581</v>
+        <v>3.2472</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6807</v>
+        <v>-1.3721</v>
       </c>
       <c r="G3" t="n">
         <v>2.0639</v>
@@ -688,13 +688,13 @@
         <v>1.7855</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8541</v>
+        <v>-0.2565</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2436</v>
+        <v>0.0454</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6105</v>
+        <v>-0.3019</v>
       </c>
       <c r="V3" t="n">
         <v>0.266</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.737</v>
+        <v>1.2636</v>
       </c>
       <c r="E4" t="n">
-        <v>1.057</v>
+        <v>1.5275</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.32</v>
+        <v>-0.2639</v>
       </c>
       <c r="G4" t="n">
         <v>0.7786</v>
@@ -766,13 +766,13 @@
         <v>0.7935</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5691000000000001</v>
+        <v>-0.0425</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3741</v>
+        <v>0.0964</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.195</v>
+        <v>-0.1389</v>
       </c>
       <c r="V4" t="n">
         <v>-0.266</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4547</v>
+        <v>0.4314</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7559</v>
+        <v>1.6766</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3013</v>
+        <v>-1.2452</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4642</v>
@@ -844,13 +844,13 @@
         <v>1.1903</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5816</v>
+        <v>0.5583</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3005</v>
+        <v>0.2212</v>
       </c>
       <c r="U5" t="n">
-        <v>0.281</v>
+        <v>0.3372</v>
       </c>
       <c r="V5" t="n">
         <v>0.3373</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4729</v>
+        <v>-0.3606</v>
       </c>
       <c r="E6" t="n">
         <v>-0.287</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1859</v>
+        <v>-0.0737</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0262</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4466</v>
+        <v>-0.3344</v>
       </c>
       <c r="T6" t="n">
         <v>-0.2494</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1973</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.64</v>
+        <v>-0.538</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.64</v>
+        <v>-0.538</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.102</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.102</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0607</v>
+        <v>-0.9485</v>
       </c>
       <c r="E8" t="n">
         <v>-0.2716</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7891</v>
+        <v>-0.6768999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5517</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.509</v>
+        <v>-0.3968</v>
       </c>
       <c r="T8" t="n">
         <v>-0.3117</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1973</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6302</v>
+        <v>-0.9713000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7393</v>
+        <v>0.0599</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8909</v>
+        <v>-1.0311</v>
       </c>
       <c r="G9" t="n">
         <v>-0.252</v>
@@ -1156,13 +1156,13 @@
         <v>1.5871</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6604</v>
+        <v>-0.0014</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9294</v>
+        <v>-0.1302</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2691</v>
+        <v>0.1288</v>
       </c>
       <c r="V9" t="n">
         <v>0.8692</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. CASTILLO EDIO</t>
+          <t>D. COFFIE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2903</v>
+        <v>-4.1947</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7469</v>
+        <v>-2.4689</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5434</v>
+        <v>-1.7257</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.7962</v>
+        <v>-3.0549</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.9789</v>
+        <v>-4.3246</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1827</v>
+        <v>1.2696</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6191</v>
+        <v>-1.2892</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.3069</v>
+        <v>-1.8591</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6879</v>
+        <v>0.5699</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.1771</v>
+        <v>-1.7657</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.6719</v>
+        <v>-2.4654</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5051</v>
+        <v>0.6997</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5952</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1903</v>
+        <v>-2.1822</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7855</v>
+        <v>0.7935</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7799</v>
+        <v>-0.6915</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0625</v>
+        <v>-0.2039</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7175</v>
+        <v>-0.4876</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.8692</v>
+        <v>0.9405</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8692</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. COFFIE</t>
+          <t>A. CASTILLO EDIO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8079</v>
+        <v>-4.4921</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6333</v>
+        <v>-2.7243</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1746</v>
+        <v>-1.7678</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.0549</v>
+        <v>-4.7962</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.3246</v>
+        <v>-4.9789</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2696</v>
+        <v>0.1827</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2892</v>
+        <v>-1.6191</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.8591</v>
+        <v>-2.3069</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5699</v>
+        <v>0.6879</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7657</v>
+        <v>-3.1771</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.4654</v>
+        <v>-2.6719</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6997</v>
+        <v>-0.5051</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3887</v>
+        <v>0.5952</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1822</v>
+        <v>-1.1903</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7935</v>
+        <v>1.7855</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3048</v>
+        <v>0.5782</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3683</v>
+        <v>0.0852</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9364</v>
+        <v>0.493</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9405</v>
+        <v>-0.8692</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.266</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9287</v>
+        <v>-4.993599999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4027</v>
+        <v>3.338000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.3316</v>
+        <v>-8.3315</v>
       </c>
       <c r="G12" t="n">
         <v>-5.417</v>
@@ -1366,7 +1366,7 @@
         <v>9.682600000000003</v>
       </c>
       <c r="K12" t="n">
-        <v>3.885899999999999</v>
+        <v>3.8859</v>
       </c>
       <c r="L12" t="n">
         <v>5.7969</v>
@@ -1390,13 +1390,13 @@
         <v>9.9192</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6234999999999999</v>
+        <v>0.3117000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8776999999999999</v>
+        <v>0.05760000000000012</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2543000000000001</v>
+        <v>0.2543</v>
       </c>
       <c r="V12" t="n">
         <v>3.0875</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.007</v>
+        <v>5.1177</v>
       </c>
       <c r="E13" t="n">
-        <v>4.8787</v>
+        <v>4.4706</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1283</v>
+        <v>0.6472</v>
       </c>
       <c r="G13" t="n">
         <v>2.7768</v>
@@ -1468,13 +1468,13 @@
         <v>1.9838</v>
       </c>
       <c r="S13" t="n">
-        <v>1.901</v>
+        <v>1.0117</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6803</v>
+        <v>0.2722</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2207</v>
+        <v>0.7395</v>
       </c>
       <c r="V13" t="n">
         <v>0.3373</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4588</v>
+        <v>3.9775</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7441</v>
+        <v>3.8462</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2853</v>
+        <v>0.1313</v>
       </c>
       <c r="G14" t="n">
         <v>2.3644</v>
@@ -1546,13 +1546,13 @@
         <v>1.5871</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2267</v>
+        <v>0.2919</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0056</v>
+        <v>0.0964</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2211</v>
+        <v>0.1955</v>
       </c>
       <c r="V14" t="n">
         <v>-0.266</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0057</v>
+        <v>3.5345</v>
       </c>
       <c r="E15" t="n">
         <v>1.6206</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3851</v>
+        <v>1.9139</v>
       </c>
       <c r="G15" t="n">
         <v>1.3341</v>
@@ -1624,13 +1624,13 @@
         <v>1.7855</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1316</v>
+        <v>0.6604</v>
       </c>
       <c r="T15" t="n">
         <v>0.1758</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0443</v>
+        <v>0.4845</v>
       </c>
       <c r="V15" t="n">
         <v>1.7384</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. BLÁZQUEZ FARRIOL</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1082</v>
+        <v>1.8312</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9105</v>
+        <v>1.4173</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1977</v>
+        <v>0.4139</v>
       </c>
       <c r="G16" t="n">
-        <v>0.27</v>
+        <v>0.2398</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7963</v>
+        <v>0.065</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0663</v>
+        <v>0.1748</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7258</v>
+        <v>0.9991</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5995</v>
+        <v>0.5847</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3253</v>
+        <v>0.4144</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4558</v>
+        <v>-0.7593</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1967</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2591</v>
+        <v>-0.2396</v>
       </c>
       <c r="P16" t="n">
         <v>0.3968</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3968</v>
+        <v>1.3887</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4414</v>
+        <v>-0.2778</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1847</v>
+        <v>-0.0623</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2567</v>
+        <v>-0.2155</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>A. BLÁZQUEZ FARRIOL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8586</v>
+        <v>1.422</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8051</v>
+        <v>1.1963</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0534</v>
+        <v>0.2258</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2398</v>
+        <v>0.27</v>
       </c>
       <c r="H17" t="n">
-        <v>0.065</v>
+        <v>-0.7963</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1748</v>
+        <v>1.0663</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9991</v>
+        <v>0.7258</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5847</v>
+        <v>-0.5995</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4144</v>
+        <v>1.3253</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7593</v>
+        <v>-0.4558</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.1967</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2396</v>
+        <v>-0.2591</v>
       </c>
       <c r="P17" t="n">
         <v>0.3968</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3887</v>
+        <v>0.3968</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2504</v>
+        <v>0.7553</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6744</v>
+        <v>0.4705</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.576</v>
+        <v>0.2848</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3959</v>
+        <v>-1.4647</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7991</v>
+        <v>-1.391</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4032</v>
+        <v>-0.0737</v>
       </c>
       <c r="G18" t="n">
         <v>1.4537</v>
@@ -1858,13 +1858,13 @@
         <v>1.1903</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3691</v>
+        <v>-0.4379</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.5894</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6284</v>
+        <v>0.1515</v>
       </c>
       <c r="V18" t="n">
         <v>-2.6789</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9021</v>
+        <v>-1.7082</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6824</v>
+        <v>-1.3763</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2196</v>
+        <v>-0.3319</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6094000000000001</v>
@@ -1936,13 +1936,13 @@
         <v>1.5871</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3106</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0057</v>
+        <v>0.3118</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3049</v>
+        <v>0.1926</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2065</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0851</v>
+        <v>-2.0749</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.903</v>
+        <v>-1.005</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1821</v>
+        <v>-1.0699</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3583</v>
@@ -2092,13 +2092,13 @@
         <v>1.5871</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.322</v>
+        <v>-0.3118</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0566</v>
+        <v>-0.1586</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2654</v>
+        <v>-0.1531</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2042</v>
+        <v>-2.1039</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7369</v>
+        <v>-0.9409</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4674</v>
+        <v>-1.163</v>
       </c>
       <c r="G22" t="n">
         <v>1.0779</v>
@@ -2170,13 +2170,13 @@
         <v>1.1903</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6076</v>
+        <v>-0.5073</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3173</v>
+        <v>-0.5214</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2903</v>
+        <v>0.0141</v>
       </c>
       <c r="V22" t="n">
         <v>-1.881</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>5.928699999999999</v>
+        <v>6.608900000000002</v>
       </c>
       <c r="E23" t="n">
-        <v>8.3315</v>
+        <v>8.331700000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4029</v>
+        <v>-1.7226</v>
       </c>
       <c r="G23" t="n">
         <v>5.417</v>
@@ -2233,10 +2233,10 @@
         <v>-9.682399999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-3.885700000000001</v>
+        <v>-3.8857</v>
       </c>
       <c r="O23" t="n">
-        <v>-5.796800000000001</v>
+        <v>-5.796799999999999</v>
       </c>
       <c r="P23" t="n">
         <v>2.975899999999999</v>
@@ -2248,13 +2248,13 @@
         <v>12.8951</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6234000000000001</v>
+        <v>1.3036</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2542999999999999</v>
+        <v>-0.2544000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8775999999999999</v>
+        <v>1.5579</v>
       </c>
       <c r="V23" t="n">
         <v>-3.0875</v>
